--- a/output/pdf_financials_xlsx/MAXX.xlsx
+++ b/output/pdf_financials_xlsx/MAXX.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MAXX.xlsx
+++ b/output/pdf_financials_xlsx/MAXX.xlsx
@@ -429,12 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,10 +453,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
@@ -484,6 +490,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -497,6 +508,9 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -514,6 +528,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -522,9 +541,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>0.628923</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>2.227429</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>4.063896</v>
       </c>
     </row>
@@ -540,6 +562,9 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -548,9 +573,12 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1.179541</v>
       </c>
       <c r="C9" s="3" t="n">
+        <v>1.380676</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -561,9 +589,12 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5.207583</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4.591279</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>13.023117</v>
       </c>
     </row>
@@ -583,6 +614,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -596,6 +632,9 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -604,10 +643,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -622,6 +664,9 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -630,9 +675,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-4.591279</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-13.023117</v>
       </c>
     </row>
@@ -643,9 +691,12 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -656,10 +707,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -678,6 +732,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -695,6 +754,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -703,9 +767,12 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -721,6 +788,9 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -734,6 +804,9 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -742,9 +815,12 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -755,9 +831,12 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-0.21</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-0.17</v>
       </c>
     </row>
@@ -768,9 +847,12 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-0.21</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-0.17</v>
       </c>
     </row>
@@ -781,9 +863,12 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>43.396525</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>56.981733</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>76.84871200000001</v>
       </c>
     </row>
@@ -794,9 +879,12 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -812,6 +900,9 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -820,9 +911,12 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -842,6 +936,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -855,6 +954,9 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -872,6 +974,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -887,9 +994,12 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0.99016</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>0.839255</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>4.726921</v>
       </c>
     </row>
@@ -905,6 +1015,9 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -913,9 +1026,12 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>0.99016</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>0.839255</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>4.726921</v>
       </c>
     </row>
@@ -931,6 +1047,9 @@
       <c r="C37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -944,6 +1063,9 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -957,6 +1079,9 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -970,6 +1095,9 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -983,6 +1111,9 @@
       <c r="C41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -996,6 +1127,9 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1009,6 +1143,9 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1022,6 +1159,9 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1035,6 +1175,9 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1048,6 +1191,9 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1061,6 +1207,9 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1069,9 +1218,12 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>0.611312</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>0.067039</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.55816</v>
       </c>
     </row>
@@ -1082,9 +1234,12 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>1.601472</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>0.906294</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>5.285081</v>
       </c>
     </row>
@@ -1100,6 +1255,9 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1113,6 +1271,9 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1126,6 +1287,9 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1139,6 +1303,9 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1152,6 +1319,9 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1169,6 +1339,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1182,6 +1357,9 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1195,6 +1373,9 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1203,9 +1384,12 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>9.153105999999999</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>1.524125</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>3.516734</v>
       </c>
     </row>
@@ -1221,6 +1405,9 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1234,6 +1421,9 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1247,6 +1437,9 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1255,9 +1448,12 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
+        <v>9.153105999999999</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>1.524125</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="D62" s="3" t="n">
         <v>3.516734</v>
       </c>
     </row>
@@ -1268,9 +1464,12 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
+        <v>10.754578</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>2.430419</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="D63" s="3" t="n">
         <v>8.801815</v>
       </c>
     </row>
@@ -1286,6 +1485,9 @@
       <c r="C64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1299,6 +1501,9 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1312,6 +1517,9 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1325,6 +1533,9 @@
       <c r="C67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1333,9 +1544,12 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
+        <v>0.400753</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>0.09542</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>1.358977</v>
       </c>
     </row>
@@ -1351,6 +1565,9 @@
       <c r="C69" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1364,6 +1581,9 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1377,6 +1597,9 @@
       <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1390,6 +1613,9 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1403,6 +1629,9 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1416,6 +1645,9 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1429,6 +1661,9 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1446,6 +1681,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1459,6 +1699,9 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1472,6 +1715,9 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1485,6 +1731,9 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1502,6 +1751,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1515,6 +1769,9 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1528,6 +1785,9 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1541,6 +1801,9 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1554,6 +1817,9 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1567,6 +1833,9 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1584,6 +1853,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1592,9 +1866,12 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
+        <v>0.400753</v>
+      </c>
+      <c r="C87" s="3" t="n">
         <v>0.09542</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="D87" s="3" t="n">
         <v>1.358977</v>
       </c>
     </row>
@@ -1605,9 +1882,12 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
+        <v>14.495463</v>
+      </c>
+      <c r="C88" s="3" t="n">
         <v>17.6473</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="D88" s="3" t="n">
         <v>32.193512</v>
       </c>
     </row>
@@ -1623,6 +1903,9 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1631,9 +1914,12 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
+        <v>-7.644829</v>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>-19.610993</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="D90" s="3" t="n">
         <v>-32.675274</v>
       </c>
     </row>
@@ -1649,6 +1935,9 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1657,9 +1946,12 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
+        <v>3.503191</v>
+      </c>
+      <c r="C92" s="3" t="n">
         <v>4.298692</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="D92" s="3" t="n">
         <v>7.9246</v>
       </c>
     </row>
@@ -1675,6 +1967,9 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -1683,9 +1978,12 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
+        <v>10.353825</v>
+      </c>
+      <c r="C94" s="3" t="n">
         <v>2.334999</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="D94" s="3" t="n">
         <v>7.422838</v>
       </c>
     </row>
@@ -1701,6 +1999,9 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1709,9 +2010,12 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
+        <v>10.353825</v>
+      </c>
+      <c r="C96" s="3" t="n">
         <v>2.334999</v>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="D96" s="3" t="n">
         <v>7.422838</v>
       </c>
     </row>
@@ -1722,9 +2026,12 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
+        <v>0.9627365202056278</v>
+      </c>
+      <c r="C97" s="3" t="n">
         <v>0.960739279934859</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="D97" s="3" t="n">
         <v>0.8433303812906769</v>
       </c>
     </row>
@@ -1742,9 +2049,12 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
+        <v>-5.207583</v>
+      </c>
+      <c r="C99" s="3" t="n">
         <v>-11.966164</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="D99" s="3" t="n">
         <v>-13.064281</v>
       </c>
     </row>
@@ -1760,6 +2070,9 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1773,6 +2086,9 @@
       <c r="C101" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -1786,6 +2102,9 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -1794,9 +2113,12 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
+        <v>-0.19685</v>
+      </c>
+      <c r="C103" s="3" t="n">
         <v>0.475239</v>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="D103" s="3" t="n">
         <v>-0.241119</v>
       </c>
     </row>
@@ -1807,9 +2129,12 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
+        <v>0.393119</v>
+      </c>
+      <c r="C104" s="3" t="n">
         <v>-0.305333</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="D104" s="3" t="n">
         <v>1.263557</v>
       </c>
     </row>
@@ -1825,6 +2150,9 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -1833,9 +2161,12 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
+        <v>0.196269</v>
+      </c>
+      <c r="C106" s="3" t="n">
         <v>0.169906</v>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="D106" s="3" t="n">
         <v>1.022438</v>
       </c>
     </row>
@@ -1846,9 +2177,12 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
+        <v>1.08305</v>
+      </c>
+      <c r="C107" s="3" t="n">
         <v>0.801912</v>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="D107" s="3" t="n">
         <v>4.118462</v>
       </c>
     </row>
@@ -1864,6 +2198,9 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -1877,6 +2214,9 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -1890,6 +2230,9 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -1903,6 +2246,9 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -1916,6 +2262,9 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -1929,6 +2278,9 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -1942,6 +2294,9 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -1955,6 +2310,9 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -1968,6 +2326,9 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -1981,6 +2342,9 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -1989,9 +2353,12 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
+        <v>-0.674305</v>
+      </c>
+      <c r="C118" s="3" t="n">
         <v>7.628981</v>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="D118" s="3" t="n">
         <v>-0.321196</v>
       </c>
     </row>
@@ -2002,9 +2369,12 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
+        <v>-0.674305</v>
+      </c>
+      <c r="C119" s="3" t="n">
         <v>-0.061164</v>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="D119" s="3" t="n">
         <v>-0.36236</v>
       </c>
     </row>
@@ -2020,6 +2390,9 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2033,6 +2406,9 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2046,6 +2422,9 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2059,6 +2438,9 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2072,6 +2454,9 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2085,6 +2470,9 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2098,6 +2486,9 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2115,6 +2506,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2123,9 +2519,12 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
+        <v>-0.030613</v>
+      </c>
+      <c r="C128" s="3" t="n">
         <v>-0.094405</v>
       </c>
-      <c r="C128" s="3" t="n">
+      <c r="D128" s="3" t="n">
         <v>-0.017499</v>
       </c>
     </row>
@@ -2136,9 +2535,12 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
+        <v>1.29369</v>
+      </c>
+      <c r="C129" s="3" t="n">
         <v>3.145426</v>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="D129" s="3" t="n">
         <v>12.382245</v>
       </c>
     </row>
@@ -2149,9 +2551,12 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
+        <v>4.351927</v>
+      </c>
+      <c r="C130" s="3" t="n">
         <v>0.99016</v>
       </c>
-      <c r="C130" s="3" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.839255</v>
       </c>
     </row>
@@ -2167,6 +2572,9 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2175,9 +2583,12 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
+        <v>-3.361767</v>
+      </c>
+      <c r="C132" s="3" t="n">
         <v>-0.150905</v>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="D132" s="3" t="n">
         <v>3.887666</v>
       </c>
     </row>
@@ -2188,9 +2599,12 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
+        <v>0.99016</v>
+      </c>
+      <c r="C133" s="3" t="n">
         <v>0.839255</v>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="D133" s="3" t="n">
         <v>4.726921</v>
       </c>
     </row>
@@ -2206,6 +2620,9 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -2214,9 +2631,12 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
+        <v>-3.981152</v>
+      </c>
+      <c r="C135" s="3" t="n">
         <v>-3.235167</v>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="D135" s="3" t="n">
         <v>-8.132218999999999</v>
       </c>
     </row>
@@ -2231,7 +2651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2263,10 +2683,15 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2294,9 +2719,12 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
+        <v>0.99016</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>0.839255</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="5" t="n">
         <v>4.726921</v>
       </c>
     </row>
@@ -2318,9 +2746,12 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="5" t="n">
+        <v>0.096021</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>0.026987</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.276989</v>
       </c>
     </row>
@@ -2346,9 +2777,12 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
+        <v>0.5152910000000001</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>0.040052</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.281171</v>
       </c>
     </row>
@@ -2374,9 +2808,12 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
+        <v>1.601472</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>0.906294</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>5.285081</v>
       </c>
     </row>
@@ -2401,10 +2838,15 @@
           <t>NetPPE</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>1.524125</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>3.516734</v>
       </c>
     </row>
@@ -2429,10 +2871,15 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>2.430419</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>8.801815</v>
       </c>
     </row>
@@ -2458,9 +2905,12 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
+        <v>0.400753</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>0.09542</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>1.358977</v>
       </c>
     </row>
@@ -2485,10 +2935,15 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>0.09542</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>1.358977</v>
       </c>
     </row>
@@ -2513,10 +2968,15 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>17.6473</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>32.193512</v>
       </c>
     </row>
@@ -2541,10 +3001,15 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>4.298692</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>7.9246</v>
       </c>
     </row>
@@ -2569,10 +3034,15 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>-19.610993</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>-32.675274</v>
       </c>
     </row>
@@ -2597,10 +3067,15 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>2.334999</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>7.422838</v>
       </c>
     </row>
@@ -2625,10 +3100,15 @@
           <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>2.430419</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>8.801815</v>
       </c>
     </row>
@@ -2638,20 +3118,31 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Current assets</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>December 31, December</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation assets (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.153105999999999</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>1.524125</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2667,21 +3158,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 839,255</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10.754578</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.99016</v>
+        <v>2.430419</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2692,22 +3186,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GST &amp; QST receivable 26,987</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.400753</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.096021</v>
+        <v>0.09542</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2718,26 +3219,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits 40,052</t>
+          <t>Share capital (Note 10)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>14.495463</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5152910000000001</v>
+        <v>17.6473</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2748,26 +3252,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (Notes 5 and 6) 1,524,125</t>
+          <t>Contributed surplus (Notes 11 &amp; 12)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>3.503191</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>9.153105999999999</v>
+        <v>4.298692</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2778,26 +3285,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total assets 2,430,419</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-7.644829</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10.754578</v>
+        <v>-19.610993</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2808,26 +3318,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 95,420</t>
+          <t>Total shareholders’ equity</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>10.353825</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.400753</v>
+        <v>2.334999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2838,47 +3351,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Total liabilities 95,420</t>
+          <t>Total liabilities and shareholders’ equity</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>10.754578</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.400753</v>
+        <v>2.430419</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share capital (Note 10) 17,647,300</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2887,175 +3403,194 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>14.495463</v>
+        <v>-11.966164</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-13.064281</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contributed surplus (Notes 11 &amp; 12) 4,298,692</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.08305</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>3.503191</v>
+        <v>0.801912</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.118462</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deficit (19,610,993)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Write-down of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-7.644829</v>
+        <v>7.690145</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.041164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity 2,334,999</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.393119</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>10.353825</v>
+        <v>-0.305333</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.263557</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity 2,430,419</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GST &amp; QST receivable</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>-0.052888</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>10.754578</v>
+        <v>0.069034</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.250002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nature of operations and going concern (Note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.19685</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.475239</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.241119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Subsequent events (Note</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.981152</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1.7e-05</v>
+        <v>-3.235167</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-8.132218999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3066,24 +3601,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-11.966164</v>
+        <v>-0.674305</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-13.064281</v>
+        <v>-0.061164</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.36236</v>
       </c>
     </row>
     <row r="31">
@@ -3094,24 +3632,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.801912</v>
+        <v>-0.674305</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>4.118462</v>
+        <v>-0.061164</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.36236</v>
       </c>
     </row>
     <row r="32">
@@ -3122,24 +3663,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets</t>
+          <t>Proceeds from issuance of common shares</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>7.690145</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.041164</v>
+        <v>3.239831</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3150,24 +3696,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Share issuance cost</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-0.305333</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.263557</v>
+        <v>-0.094405</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.017499</v>
       </c>
     </row>
     <row r="34">
@@ -3178,20 +3729,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GST &amp; QST receivable</t>
+          <t>Proceeds from warrant exercises</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.069034</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>-0.250002</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>2.644869</v>
       </c>
     </row>
     <row r="35">
@@ -3202,24 +3760,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Proceeds from stock-option exercises</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.475239</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-0.241119</v>
+          <t>ProceedsFromStockOptionExercised</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.159375</v>
       </c>
     </row>
     <row r="36">
@@ -3230,24 +3795,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>-3.235167</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-8.132218999999999</v>
+          <t>Obligation to issue shares</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.1455</v>
       </c>
     </row>
     <row r="37">
@@ -3258,24 +3826,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-0.061164</v>
+        <v>1.29369</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.36236</v>
+        <v>3.145426</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>12.382245</v>
       </c>
     </row>
     <row r="38">
@@ -3286,24 +3857,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Increase (decrease) in cash</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.061164</v>
+        <v>-3.361767</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.36236</v>
+        <v>-0.150905</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>3.887666</v>
       </c>
     </row>
     <row r="39">
@@ -3319,19 +3893,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>3.239831</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>9.449999999999999</v>
+        <v>0.99016</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.839255</v>
       </c>
     </row>
     <row r="40">
@@ -3347,19 +3926,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Share issuance cost</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>-0.094405</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.017499</v>
+        <v>0.839255</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>4.726921</v>
       </c>
     </row>
     <row r="41">
@@ -3370,22 +3954,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Proceeds from warrant exercises</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-5.207583</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2.644869</v>
+        <v>-11.966164</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3401,21 +3992,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Proceeds from stock-option exercises</t>
+          <t>Proceeds from issuance of shares</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ProceedsFromStockOptionExercised</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>1.324303</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.159375</v>
+        <v>3.239831</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3431,17 +4025,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Obligation to issue shares</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-0.030613</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.1455</v>
+        <v>-0.094405</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3457,19 +4058,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, beginning of the period</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3.145426</v>
+        <v>4.351927</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>12.382245</v>
+        <v>0.99016</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3485,75 +4091,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
+          <t>Cash, end of period</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-0.150905</v>
+        <v>0.99016</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>3.887666</v>
+        <v>0.839255</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Ended</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash, beginning of theyear</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.99016</v>
+          <t>Ended total</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.839255</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash, end ofyear</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.839255</v>
+        <v>0.045716</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>4.726921</v>
+        <v>0.059606</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.348867</v>
       </c>
     </row>
     <row r="48">
@@ -3564,20 +4179,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ended</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ended total</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Consulting fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.501949</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.6774210000000001</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1.196729</v>
       </c>
     </row>
     <row r="49">
@@ -3593,19 +4215,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Exploration expenses (Note 7)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>0.059606</v>
+        <v>1.806474</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.348867</v>
+        <v>1.19362</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>4.463962</v>
       </c>
     </row>
     <row r="50">
@@ -3621,19 +4242,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>0.6774210000000001</v>
+          <t>Research and development costs (recovery) (Note 8)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1.196729</v>
+        <v>0.255567</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.011605</v>
       </c>
     </row>
     <row r="51">
@@ -3649,15 +4271,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Exploration expenses (Note 7)</t>
+          <t>Exchange &amp; filing fees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>1.19362</v>
+        <v>0.057194</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>4.463962</v>
+        <v>0.053145</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.039535</v>
       </c>
     </row>
     <row r="52">
@@ -3673,15 +4298,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Research and development costs (recovery) (Note 8)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.255567</v>
+          <t>Office &amp; miscellaneous (Note 9)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.011605</v>
+        <v>0.040134</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.201456</v>
       </c>
     </row>
     <row r="53">
@@ -3697,15 +4331,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exchange &amp; filing fees</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.053145</v>
+          <t>Advertising, promotion &amp; investor relations</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.039535</v>
+        <v>1.441176</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.550688</v>
       </c>
     </row>
     <row r="54">
@@ -3721,19 +4364,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Office &amp; miscellaneous (Note 9)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.040134</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.201456</v>
+        <v>0.801912</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>4.118462</v>
       </c>
     </row>
     <row r="55">
@@ -3749,7 +4393,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Advertising, promotion &amp; investor relations</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3758,10 +4402,13 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1.441176</v>
+        <v>0.07818</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>2.550688</v>
+        <v>0.068698</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.115023</v>
       </c>
     </row>
     <row r="56">
@@ -3777,15 +4424,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>0.801912</v>
+        <v>5.207583</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>4.118462</v>
+        <v>4.591279</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>13.023117</v>
       </c>
     </row>
     <row r="57">
@@ -3801,19 +4455,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Net loss before other income</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.068698</v>
+        <v>-5.207583</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.115023</v>
+        <v>-4.591279</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-13.023117</v>
       </c>
     </row>
     <row r="58">
@@ -3829,19 +4486,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>4.591279</v>
+          <t>Write-down of exploration and evaluation assets (Note 5)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>13.023117</v>
+        <v>-7.690145</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.041164</v>
       </c>
     </row>
     <row r="59">
@@ -3857,19 +4515,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net loss before other income</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>-4.591279</v>
+          <t>Interest revenues</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-13.023117</v>
+        <v>0.005722</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3885,15 +4546,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Note 5)</t>
+          <t>Quebec exploration refund (Note 4)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>-7.690145</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.041164</v>
+        <v>0.309538</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3909,17 +4577,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Interest revenues</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
-        <v>0.005722</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.207583</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-11.966164</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-13.064281</v>
       </c>
     </row>
     <row r="62">
@@ -3935,17 +4608,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Quebec exploration refund (Note 4)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
-        <v>0.309538</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.2e-07</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-2.1e-07</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
     </row>
     <row r="63">
@@ -3961,19 +4639,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Weighted average shares outstanding</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>-11.966164</v>
+        <v>44.672573</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-13.064281</v>
+        <v>56.350264</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>78.28377999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3989,19 +4670,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Research and development costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>-2.1e-07</v>
+        <v>0.406685</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>0.255567</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4017,19 +4699,117 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>56.350264</v>
+          <t>Market making services</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>78.28377999999999</v>
+        <v>0.0605</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Office &amp; miscellaneous</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.048794</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.040134</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1.179541</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1.380676</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 12)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>1.08305</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.801912</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/MAXX.xlsx
+++ b/output/pdf_financials_xlsx/MAXX.xlsx
@@ -4518,7 +4518,11 @@
           <t>Interest revenues</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
